--- a/data/trans_camb/P26-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P26-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 12,74</t>
+          <t>-3,96; 13,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 9,42</t>
+          <t>-8,18; 8,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,83; -6,36</t>
+          <t>-21,98; -4,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 9,24</t>
+          <t>-9,49; 9,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 5,61</t>
+          <t>-13,28; 4,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,2; -11,06</t>
+          <t>-28,13; -11,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 9,33</t>
+          <t>-4,24; 9,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 5,32</t>
+          <t>-7,34; 5,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-22,96; -10,84</t>
+          <t>-23,24; -10,77</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 43,98</t>
+          <t>-10,52; 45,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 33,55</t>
+          <t>-21,28; 29,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,19; -19,87</t>
+          <t>-60,04; -14,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,09; 23,8</t>
+          <t>-20,56; 24,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 14,34</t>
+          <t>-27,98; 12,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,89; -29,09</t>
+          <t>-59,36; -29,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 27,36</t>
+          <t>-10,42; 27,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 15,33</t>
+          <t>-18,44; 14,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-56,53; -31,31</t>
+          <t>-57,37; -30,76</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 13,22</t>
+          <t>0,82; 13,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 3,25</t>
+          <t>-8,28; 3,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,18; -8,59</t>
+          <t>-21,08; -8,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 13,55</t>
+          <t>0,82; 14,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 5,21</t>
+          <t>-6,38; 5,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,03; -15,83</t>
+          <t>-26,17; -16,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 11,8</t>
+          <t>3,39; 12,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 3,07</t>
+          <t>-5,41; 3,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-21,83; -14,2</t>
+          <t>-22,17; -14,47</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 59,12</t>
+          <t>2,55; 60,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 14,46</t>
+          <t>-28,98; 15,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-76,32; -36,71</t>
+          <t>-76,86; -37,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 44,9</t>
+          <t>2,34; 46,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 16,99</t>
+          <t>-17,72; 18,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,26; -51,52</t>
+          <t>-71,25; -51,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,7; 42,64</t>
+          <t>10,54; 46,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 11,44</t>
+          <t>-17,18; 11,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-70,2; -51,2</t>
+          <t>-70,15; -51,91</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 15,88</t>
+          <t>1,01; 16,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,02; -2,1</t>
+          <t>-16,02; -3,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,85; -14,7</t>
+          <t>-26,37; -14,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 5,5</t>
+          <t>-9,55; 5,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,48; -18,25</t>
+          <t>-31,86; -18,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,1; -16,2</t>
+          <t>-29,68; -15,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 8,47</t>
+          <t>-2,18; 8,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,47; -11,9</t>
+          <t>-21,66; -12,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,02; -16,77</t>
+          <t>-25,72; -17,15</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,55; 68,21</t>
+          <t>2,26; 68,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,99; -8,98</t>
+          <t>-51,84; -12,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,82; -61,19</t>
+          <t>-84,68; -62,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,93; 16,24</t>
+          <t>-23,34; 15,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-74,53; -52,85</t>
+          <t>-75,1; -52,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,69; -46,41</t>
+          <t>-70,3; -46,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 28,22</t>
+          <t>-6,38; 26,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-61,16; -40,25</t>
+          <t>-60,91; -40,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-73,31; -56,13</t>
+          <t>-72,59; -55,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 7,37</t>
+          <t>-6,42; 7,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 7,01</t>
+          <t>-7,34; 6,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,18; -5,56</t>
+          <t>-21,12; -6,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-19,89; -5,82</t>
+          <t>-19,56; -5,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,7; -6,08</t>
+          <t>-19,75; -5,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-39,97; -25,98</t>
+          <t>-40,39; -26,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,1; -1,08</t>
+          <t>-11,46; -1,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,73; -1,43</t>
+          <t>-11,29; -1,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-28,64; -18,72</t>
+          <t>-28,67; -18,79</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 28,8</t>
+          <t>-20,25; 30,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 27,99</t>
+          <t>-23,27; 26,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-67,37; -19,74</t>
+          <t>-68,11; -23,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,82; -15,06</t>
+          <t>-43,03; -13,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,95; -15,52</t>
+          <t>-44,11; -13,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,72; -67,05</t>
+          <t>-87,56; -66,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,63; -3,43</t>
+          <t>-29,46; -3,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,84; -4,34</t>
+          <t>-29,92; -4,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-77,3; -56,21</t>
+          <t>-77,16; -55,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 15,06</t>
+          <t>-4,97; 13,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 8,09</t>
+          <t>-10,03; 7,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-31,09; -15,8</t>
+          <t>-31,64; -16,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 18,85</t>
+          <t>-0,2; 19,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,89; -0,14</t>
+          <t>-17,91; 0,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-32,16; -16,79</t>
+          <t>-31,26; -16,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 14,02</t>
+          <t>-0,13; 14,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 1,21</t>
+          <t>-11,48; 1,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-28,98; -18,83</t>
+          <t>-29,45; -19,12</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 63,61</t>
+          <t>-14,6; 59,29</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,46; 35,95</t>
+          <t>-30,14; 33,74</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-93,33; -64,96</t>
+          <t>-94,15; -67,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,25; 73,77</t>
+          <t>-0,66; 79,13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-49,12; 0,12</t>
+          <t>-49,14; 1,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-86,56; -67,18</t>
+          <t>-85,95; -65,86</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,93; 54,17</t>
+          <t>-0,51; 56,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-35,22; 4,72</t>
+          <t>-35,6; 5,68</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-87,41; -72,13</t>
+          <t>-87,38; -72,88</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 10,97</t>
+          <t>-6,12; 10,32</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 4,02</t>
+          <t>-11,98; 3,41</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-23,71; -10,21</t>
+          <t>-24,98; -11,26</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 13,05</t>
+          <t>-4,5; 12,27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-17,77; -1,26</t>
+          <t>-17,88; -0,32</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-35,17; -20,8</t>
+          <t>-35,13; -20,34</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 8,75</t>
+          <t>-2,62; 8,89</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,74; -1,48</t>
+          <t>-12,41; -1,24</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-27,87; -17,44</t>
+          <t>-26,92; -17,12</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 45,67</t>
+          <t>-19,16; 43,15</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-38,3; 16,78</t>
+          <t>-37,33; 14,86</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-73,22; -41,98</t>
+          <t>-75,88; -44,04</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 38,79</t>
+          <t>-10,2; 35,61</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-41,79; -3,76</t>
+          <t>-42,17; -1,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-79,63; -58,11</t>
+          <t>-78,73; -58,65</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 28,76</t>
+          <t>-7,49; 28,16</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-35,39; -5,07</t>
+          <t>-33,96; -3,89</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-74,06; -56,11</t>
+          <t>-74,03; -54,76</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 9,06</t>
+          <t>-1,47; 9,09</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 2,02</t>
+          <t>-9,21; 1,57</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,49; -5,27</t>
+          <t>-16,23; -5,34</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 9,47</t>
+          <t>-1,99; 9,86</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,29; -2,38</t>
+          <t>-13,8; -2,79</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-31,72; -13,1</t>
+          <t>-34,3; -13,48</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 7,63</t>
+          <t>-0,03; 7,64</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-9,81; -1,85</t>
+          <t>-9,52; -2,11</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-23,53; -11,26</t>
+          <t>-24,34; -11,53</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 33,25</t>
+          <t>-4,78; 31,54</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 6,98</t>
+          <t>-27,15; 5,65</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-49,67; -18,41</t>
+          <t>-48,32; -16,57</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 26,68</t>
+          <t>-4,55; 28,55</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-32,25; -6,33</t>
+          <t>-33,81; -7,6</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-78,83; -35,65</t>
+          <t>-79,9; -35,69</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 23,33</t>
+          <t>-0,37; 23,31</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-26,92; -5,56</t>
+          <t>-25,82; -6,38</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-65,89; -34,15</t>
+          <t>-67,45; -33,82</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 7,43</t>
+          <t>-1,94; 8,15</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-10,55; -0,88</t>
+          <t>-9,68; -0,26</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 38,68</t>
+          <t>-24,14; 42,27</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 6,85</t>
+          <t>-3,06; 7,12</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-18,78; -9,51</t>
+          <t>-18,84; -9,1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-32,28; -24,24</t>
+          <t>-32,61; -24,79</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 5,94</t>
+          <t>-1,33; 5,74</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-13,07; -6,43</t>
+          <t>-13,17; -6,65</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 17,52</t>
+          <t>-26,23; 27,49</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 28,72</t>
+          <t>-6,38; 31,26</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-33,88; -3,28</t>
+          <t>-31,61; -0,93</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-81,18; 143,61</t>
+          <t>-81,61; 156,32</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 21,48</t>
+          <t>-8,28; 22,31</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-50,31; -29,5</t>
+          <t>-50,5; -28,57</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-86,69; -75,86</t>
+          <t>-87,46; -76,5</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 19,72</t>
+          <t>-4,61; 18,72</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-39,12; -22,06</t>
+          <t>-39,41; -22,05</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-82,79; 58,34</t>
+          <t>-82,27; 93,01</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,67</t>
+          <t>1,84; 6,53</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-5,71; -0,96</t>
+          <t>-5,73; -1,16</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 10,12</t>
+          <t>-17,5; 7,46</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,14</t>
+          <t>-0,96; 4,22</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-12,79; -8,17</t>
+          <t>-12,63; -7,91</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-26,88; -21,91</t>
+          <t>-27,27; -21,99</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,59</t>
+          <t>1,25; 4,77</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-8,53; -5,36</t>
+          <t>-8,51; -5,23</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-21,01; -6,08</t>
+          <t>-21,23; -6,26</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>6,98; 24,33</t>
+          <t>6,17; 23,85</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-19,11; -3,51</t>
+          <t>-19,14; -4,44</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-59,93; 35,66</t>
+          <t>-60,93; 25,05</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 11,53</t>
+          <t>-2,52; 11,97</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-33,19; -22,59</t>
+          <t>-32,98; -22,4</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-71,9; -61,01</t>
+          <t>-72,0; -60,76</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,78; 14,43</t>
+          <t>3,62; 14,87</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-25,33; -16,61</t>
+          <t>-25,31; -16,4</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-63,74; -18,62</t>
+          <t>-63,98; -19,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P26-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P26-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-14,57</t>
+          <t>-16,93</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-20,14</t>
+          <t>-22,02</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-17,29</t>
+          <t>-19,36</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 13,01</t>
+          <t>-3,45; 13,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 8,5</t>
+          <t>-8,27; 9,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,98; -4,57</t>
+          <t>-24,92; -9,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 9,21</t>
+          <t>-9,42; 9,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 4,69</t>
+          <t>-12,82; 4,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,13; -11,32</t>
+          <t>-30,27; -14,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 9,39</t>
+          <t>-3,44; 8,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 5,12</t>
+          <t>-7,94; 4,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-23,24; -10,77</t>
+          <t>-25,16; -13,74</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-43,46%</t>
+          <t>-50,48%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-47,29%</t>
+          <t>-51,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-45,57%</t>
+          <t>-51,03%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 45,17</t>
+          <t>-9,17; 45,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,28; 29,89</t>
+          <t>-22,16; 32,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-60,04; -14,84</t>
+          <t>-64,76; -28,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 24,42</t>
+          <t>-19,73; 24,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,98; 12,98</t>
+          <t>-26,85; 13,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,36; -29,14</t>
+          <t>-62,57; -36,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 27,51</t>
+          <t>-8,26; 24,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 14,99</t>
+          <t>-19,55; 13,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-57,37; -30,76</t>
+          <t>-60,2; -39,03</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-15,45</t>
+          <t>-16,09</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-20,89</t>
+          <t>-21,29</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-18,17</t>
+          <t>-18,66</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 13,31</t>
+          <t>0,87; 13,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 3,37</t>
+          <t>-8,45; 3,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,08; -8,78</t>
+          <t>-21,1; -9,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 14,18</t>
+          <t>0,5; 13,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 5,38</t>
+          <t>-6,47; 5,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,17; -16,04</t>
+          <t>-26,37; -16,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 12,3</t>
+          <t>2,94; 11,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 3,1</t>
+          <t>-5,58; 2,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-22,17; -14,47</t>
+          <t>-22,5; -14,58</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-60,81%</t>
+          <t>-63,32%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-62,19%</t>
+          <t>-63,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-61,63%</t>
+          <t>-63,29%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 60,32</t>
+          <t>3,07; 60,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,98; 15,29</t>
+          <t>-28,75; 14,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-76,86; -37,76</t>
+          <t>-76,81; -39,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 46,23</t>
+          <t>1,34; 43,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 18,25</t>
+          <t>-17,63; 17,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,25; -51,72</t>
+          <t>-72,18; -52,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,54; 46,05</t>
+          <t>8,99; 42,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 11,7</t>
+          <t>-17,45; 9,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-70,15; -51,91</t>
+          <t>-71,47; -53,19</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-20,48</t>
+          <t>-19,22</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-22,67</t>
+          <t>-22,96</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-21,44</t>
+          <t>-20,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 16,57</t>
+          <t>1,3; 15,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,02; -3,06</t>
+          <t>-15,03; -1,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,37; -14,78</t>
+          <t>-24,99; -13,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 5,33</t>
+          <t>-10,13; 5,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,86; -18,26</t>
+          <t>-31,58; -18,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,68; -15,93</t>
+          <t>-30,07; -16,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 8,21</t>
+          <t>-2,27; 8,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,66; -12,32</t>
+          <t>-21,53; -11,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-25,72; -17,15</t>
+          <t>-25,27; -16,87</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-75,53%</t>
+          <t>-70,89%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-59,36%</t>
+          <t>-60,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-65,56%</t>
+          <t>-64,04%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,26; 68,28</t>
+          <t>4,18; 68,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,84; -12,12</t>
+          <t>-49,42; -8,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,68; -62,67</t>
+          <t>-81,59; -56,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,34; 15,4</t>
+          <t>-24,04; 16,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,1; -52,82</t>
+          <t>-75,81; -52,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,3; -46,63</t>
+          <t>-70,29; -48,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 26,83</t>
+          <t>-6,31; 28,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-60,91; -40,18</t>
+          <t>-60,92; -39,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-72,59; -55,79</t>
+          <t>-71,68; -55,79</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-13,97</t>
+          <t>-14,24</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-32,54</t>
+          <t>-29,22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-23,84</t>
+          <t>-21,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 7,97</t>
+          <t>-7,04; 7,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 6,76</t>
+          <t>-6,78; 7,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,12; -6,25</t>
+          <t>-20,78; -6,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-19,56; -5,37</t>
+          <t>-19,23; -5,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,75; -5,04</t>
+          <t>-19,91; -5,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-40,39; -26,03</t>
+          <t>-35,72; -23,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,46; -1,1</t>
+          <t>-11,18; -1,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -1,51</t>
+          <t>-11,41; -1,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-28,67; -18,79</t>
+          <t>-26,61; -16,3</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-48,75%</t>
+          <t>-49,7%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-77,22%</t>
+          <t>-69,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-67,37%</t>
+          <t>-61,56%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 30,99</t>
+          <t>-21,85; 29,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 26,99</t>
+          <t>-21,49; 28,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-68,11; -23,36</t>
+          <t>-67,95; -24,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,03; -13,47</t>
+          <t>-42,63; -14,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,11; -13,29</t>
+          <t>-44,47; -14,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,56; -66,31</t>
+          <t>-76,88; -57,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,46; -3,0</t>
+          <t>-29,35; -3,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,92; -4,31</t>
+          <t>-30,14; -4,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-77,16; -55,18</t>
+          <t>-70,46; -49,56</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-24,0</t>
+          <t>-23,26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-23,86</t>
+          <t>-24,07</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-23,85</t>
+          <t>-23,64</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 13,83</t>
+          <t>-4,7; 14,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 7,96</t>
+          <t>-9,85; 8,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-31,64; -16,87</t>
+          <t>-30,97; -16,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 19,53</t>
+          <t>-0,21; 19,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 0,06</t>
+          <t>-17,9; -0,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-31,26; -16,77</t>
+          <t>-31,81; -16,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 14,46</t>
+          <t>0,41; 14,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 1,52</t>
+          <t>-11,2; 1,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-29,45; -19,12</t>
+          <t>-28,61; -18,11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-84,85%</t>
+          <t>-82,22%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-78,57%</t>
+          <t>-79,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-81,24%</t>
+          <t>-80,53%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 59,29</t>
+          <t>-14,17; 64,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,14; 33,74</t>
+          <t>-29,8; 37,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-94,15; -67,35</t>
+          <t>-91,41; -63,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 79,13</t>
+          <t>-0,69; 75,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-49,14; 1,86</t>
+          <t>-48,9; 0,04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-85,95; -65,86</t>
+          <t>-86,65; -67,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 56,46</t>
+          <t>0,91; 54,58</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 5,68</t>
+          <t>-34,19; 6,13</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-87,38; -72,88</t>
+          <t>-86,31; -70,63</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-17,15</t>
+          <t>-16,75</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-27,68</t>
+          <t>-28,11</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-22,38</t>
+          <t>-22,4</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 10,32</t>
+          <t>-6,27; 9,6</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 3,41</t>
+          <t>-12,46; 3,97</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-24,98; -11,26</t>
+          <t>-23,96; -10,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 12,27</t>
+          <t>-4,95; 12,67</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-17,88; -0,32</t>
+          <t>-18,31; -0,87</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-35,13; -20,34</t>
+          <t>-34,53; -20,66</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 8,89</t>
+          <t>-2,85; 9,18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,41; -1,24</t>
+          <t>-13,16; -1,43</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-26,92; -17,12</t>
+          <t>-27,41; -17,48</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-60,92%</t>
+          <t>-59,49%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-70,03%</t>
+          <t>-71,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-66,21%</t>
+          <t>-66,25%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 43,15</t>
+          <t>-19,05; 40,67</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-37,33; 14,86</t>
+          <t>-38,18; 17,08</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-75,88; -44,04</t>
+          <t>-72,75; -40,7</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 35,61</t>
+          <t>-11,17; 37,34</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-42,17; -1,79</t>
+          <t>-41,78; -2,55</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-78,73; -58,65</t>
+          <t>-79,27; -59,15</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 28,16</t>
+          <t>-7,86; 29,94</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-33,96; -3,89</t>
+          <t>-35,44; -4,32</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-74,03; -54,76</t>
+          <t>-73,97; -56,77</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-11,05</t>
+          <t>-11,5</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-20,72</t>
+          <t>-15,9</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-16,06</t>
+          <t>-13,65</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 9,09</t>
+          <t>-1,75; 9,46</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 1,57</t>
+          <t>-8,86; 2,45</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,23; -5,34</t>
+          <t>-16,4; -5,92</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 9,86</t>
+          <t>-2,29; 9,53</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,8; -2,79</t>
+          <t>-13,49; -2,29</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-34,3; -13,48</t>
+          <t>-20,58; -10,84</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 7,64</t>
+          <t>-0,2; 7,67</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-9,52; -2,11</t>
+          <t>-9,75; -2,14</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-24,34; -11,53</t>
+          <t>-17,04; -9,59</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-36,31%</t>
+          <t>-37,79%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-53,93%</t>
+          <t>-41,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-46,61%</t>
+          <t>-39,61%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 31,54</t>
+          <t>-5,42; 34,49</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 5,65</t>
+          <t>-26,76; 8,93</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-48,32; -16,57</t>
+          <t>-50,36; -21,15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 28,55</t>
+          <t>-5,67; 26,29</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-33,81; -7,6</t>
+          <t>-32,83; -6,47</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-79,9; -35,69</t>
+          <t>-49,61; -30,02</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 23,31</t>
+          <t>-0,56; 23,24</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-25,82; -6,38</t>
+          <t>-26,87; -6,56</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-67,45; -33,82</t>
+          <t>-47,46; -29,49</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4,31</t>
+          <t>-22,73</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-28,48</t>
+          <t>-28,71</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-10,09</t>
+          <t>-25,79</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 8,15</t>
+          <t>-2,04; 8,27</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,68; -0,26</t>
+          <t>-9,86; -0,33</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 42,27</t>
+          <t>-26,73; -18,49</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 7,12</t>
+          <t>-2,83; 7,17</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-18,84; -9,1</t>
+          <t>-18,33; -9,04</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-32,61; -24,79</t>
+          <t>-32,96; -24,91</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 5,74</t>
+          <t>-0,86; 6,13</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-13,17; -6,65</t>
+          <t>-12,95; -6,48</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-26,23; 27,49</t>
+          <t>-28,65; -23,05</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>-79,7%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-82,41%</t>
+          <t>-83,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-31,9%</t>
+          <t>-81,58%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 31,26</t>
+          <t>-6,82; 32,34</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-31,61; -0,93</t>
+          <t>-31,37; -1,25</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-81,61; 156,32</t>
+          <t>-86,26; -70,97</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 22,31</t>
+          <t>-7,6; 22,15</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-50,5; -28,57</t>
+          <t>-50,92; -28,52</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-87,46; -76,5</t>
+          <t>-87,56; -77,78</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 18,72</t>
+          <t>-2,67; 20,39</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-39,41; -22,05</t>
+          <t>-38,79; -21,77</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-82,27; 93,01</t>
+          <t>-85,6; -76,93</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-10,14</t>
+          <t>-17,18</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-24,21</t>
+          <t>-23,37</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-17,28</t>
+          <t>-20,27</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,53</t>
+          <t>1,96; 6,52</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-5,73; -1,16</t>
+          <t>-5,51; -1,01</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 7,46</t>
+          <t>-19,49; -15,0</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,22</t>
+          <t>-1,06; 3,97</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-12,63; -7,91</t>
+          <t>-12,87; -8,28</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-27,27; -21,99</t>
+          <t>-25,49; -21,35</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,77</t>
+          <t>1,24; 4,56</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-8,51; -5,23</t>
+          <t>-8,42; -5,07</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-21,23; -6,26</t>
+          <t>-21,65; -18,66</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-35,41%</t>
+          <t>-60,0%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-65,27%</t>
+          <t>-63,02%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-52,56%</t>
+          <t>-61,63%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>6,17; 23,85</t>
+          <t>6,5; 23,36</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-19,14; -4,44</t>
+          <t>-18,62; -3,71</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-60,93; 25,05</t>
+          <t>-65,17; -54,15</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 11,97</t>
+          <t>-2,72; 10,95</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-32,98; -22,4</t>
+          <t>-33,48; -22,9</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-72,0; -60,76</t>
+          <t>-66,3; -59,52</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,62; 14,87</t>
+          <t>3,76; 14,33</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-25,31; -16,4</t>
+          <t>-25,02; -15,89</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-63,98; -19,64</t>
+          <t>-64,36; -58,43</t>
         </is>
       </c>
     </row>
